--- a/nmoreau/ig/CodeSystem-preadmission-statuts-cs.xlsx
+++ b/nmoreau/ig/CodeSystem-preadmission-statuts-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T16:12:30+00:00</t>
+    <t>2025-05-26T06:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/CodeSystem-preadmission-statuts-cs.xlsx
+++ b/nmoreau/ig/CodeSystem-preadmission-statuts-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T06:59:47+00:00</t>
+    <t>2025-06-02T15:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/CodeSystem-preadmission-statuts-cs.xlsx
+++ b/nmoreau/ig/CodeSystem-preadmission-statuts-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T15:02:23+00:00</t>
+    <t>2025-10-22T09:09:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/CodeSystem-preadmission-statuts-cs.xlsx
+++ b/nmoreau/ig/CodeSystem-preadmission-statuts-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-22T09:09:51+00:00</t>
+    <t>2025-10-28T10:00:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/CodeSystem-preadmission-statuts-cs.xlsx
+++ b/nmoreau/ig/CodeSystem-preadmission-statuts-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T10:00:18+00:00</t>
+    <t>2025-11-19T09:47:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/CodeSystem-preadmission-statuts-cs.xlsx
+++ b/nmoreau/ig/CodeSystem-preadmission-statuts-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T09:47:12+00:00</t>
+    <t>2026-01-14T12:51:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/CodeSystem-preadmission-statuts-cs.xlsx
+++ b/nmoreau/ig/CodeSystem-preadmission-statuts-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T12:51:21+00:00</t>
+    <t>2026-02-24T09:27:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
